--- a/models/JL-2.xlsx
+++ b/models/JL-2.xlsx
@@ -645,12 +645,14 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>41318</v>
+        <v>49718</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14897</v>
-      </c>
-      <c r="F7" s="4" t="n"/>
+        <v>23297</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>8400</v>
+      </c>
       <c r="G7" s="4" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -675,7 +677,9 @@
       <c r="E8" s="4" t="n">
         <v>13110</v>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="4" t="n">
+        <v>7392</v>
+      </c>
       <c r="G8" s="4" t="n"/>
       <c r="I8" s="5" t="inlineStr"/>
     </row>
@@ -696,7 +700,9 @@
       <c r="E9" s="4" t="n">
         <v>1788</v>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="4" t="n">
+        <v>1008</v>
+      </c>
       <c r="G9" s="4" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -721,7 +727,9 @@
       <c r="E10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G10" s="4" t="n"/>
       <c r="I10" s="5" t="inlineStr"/>
     </row>
@@ -742,7 +750,9 @@
       <c r="E11" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="4" t="n">
+        <v>2.11</v>
+      </c>
       <c r="G11" s="4" t="n"/>
       <c r="I11" s="5" t="inlineStr"/>
     </row>
@@ -758,12 +768,14 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1292033</v>
+        <v>1314920</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>728514</v>
-      </c>
-      <c r="F12" s="4" t="n"/>
+        <v>1314920</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1065085</v>
+      </c>
       <c r="G12" s="4" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -783,12 +795,14 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>48</v>
+        <v>47.1645505490343</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F13" s="4" t="n"/>
+        <v>26.59377608725181</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>18.51225383079049</v>
+      </c>
       <c r="G13" s="4" t="n"/>
       <c r="I13" s="5" t="inlineStr"/>
     </row>
@@ -809,7 +823,9 @@
       <c r="E14" s="4" t="n">
         <v>272</v>
       </c>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="4" t="n">
+        <v>272</v>
+      </c>
       <c r="G14" s="4" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -829,12 +845,14 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="4" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -865,7 +883,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -917,7 +935,9 @@
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="4" t="n"/>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G18" s="4" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>

--- a/models/JL-2.xlsx
+++ b/models/JL-2.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>49718</v>
+        <v>50016</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>23297</v>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
     </row>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Parabola</t>
+        </is>
+      </c>
       <c r="I64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
@@ -1704,7 +1708,7 @@
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
     </row>

--- a/models/JL-2.xlsx
+++ b/models/JL-2.xlsx
@@ -1602,14 +1602,14 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SHROUD / FAIRING</t>
+          <t>FAIRING</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Shroud mass</t>
+          <t>Fairing mass</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>0 = no shroud</t>
+          <t>0 = no fairing</t>
         </is>
       </c>
     </row>
@@ -1642,14 +1642,14 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Default 80 km</t>
+          <t>Default 80 km; SLBM water-egress fairings shed low (~2 km)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Shroud length</t>
+          <t>Fairing length</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -1665,7 +1665,7 @@
     <row r="63">
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Shroud diameter</t>
+          <t>Fairing diameter</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="64">
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Shroud nose shape</t>
+          <t>Fairing nose shape</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="65">
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Shroud nose length</t>
+          <t>Fairing nose length</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
